--- a/TBD_Teacher_Assignments.xlsx
+++ b/TBD_Teacher_Assignments.xlsx
@@ -7,9 +7,12 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="TBD Teacher Assignments" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Section Assignments" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Teacher List" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="TeacherList">'Teacher List'!$A$2:$A$57</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -17,13 +20,29 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="14">
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00C00000"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -38,29 +57,20 @@
     </font>
     <font>
       <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00C00000"/>
-      <sz val="10"/>
+      <i val="1"/>
+      <color rgb="00888888"/>
+      <sz val="9"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <sz val="10"/>
+      <color rgb="000000FF"/>
+      <sz val="11"/>
     </font>
     <font>
       <name val="Arial"/>
       <color rgb="000000FF"/>
-      <sz val="11"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -70,34 +80,21 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="002F5496"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="Arial"/>
-      <i val="1"/>
-      <color rgb="00555555"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Arial"/>
       <b val="1"/>
-      <color rgb="000000FF"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
-      <color rgb="000000FF"/>
+      <color rgb="002F5496"/>
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -111,7 +108,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
+        <fgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
     <fill>
@@ -121,17 +123,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00808080"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
   </fills>
@@ -153,60 +155,49 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -572,23 +563,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H29"/>
+  <dimension ref="A1:K54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="45" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="38" customWidth="1" min="7" max="7"/>
-    <col width="45" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="35" customWidth="1" min="9" max="9"/>
+    <col width="35" customWidth="1" min="10" max="10"/>
+    <col width="35" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>TBD TEACHER ASSIGNMENTS — ACTION REQUIRED</t>
+          <t>TBD TEACHER ASSIGNMENTS — SELECT FROM DROPDOWN</t>
         </is>
       </c>
     </row>
@@ -602,19 +596,20 @@
     <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Fill in the YELLOW cells with the confirmed teacher name for each placeholder. If a placeholder represents a SINGLE hire, enter the name once — it will apply to all their courses.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="30" customHeight="1">
+          <t>For each row: click the yellow ASSIGN TEACHER cell → select a name from the dropdown. If assigning a NEW HIRE not on the list, select "NEW HIRE" and type the full name (Last, First) in the NOTES column.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>Course
+Code</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Current Placeholder</t>
+          <t>Course Title</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -624,438 +619,2191 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Courses Assigned</t>
+          <t>Type</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
+          <t>Level</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>Section #</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>Semester</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>Cap</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>CURRENT
+(TBD Placeholder)</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>ASSIGN TEACHER
+(Select from Dropdown)</t>
+        </is>
+      </c>
+      <c r="K5" s="4" t="inlineStr">
+        <is>
+          <t>NOTES</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>British Literature</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>Full-Year</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>Fall &amp; Spring</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="I6" s="7" t="inlineStr">
+        <is>
+          <t>New ENGLISH Teacher (TBD)</t>
+        </is>
+      </c>
+      <c r="J6" s="8" t="n"/>
+      <c r="K6" s="9" t="n"/>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>British Literature</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>Full-Year</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>Fall &amp; Spring</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="I7" s="7" t="inlineStr">
+        <is>
+          <t>New ENGLISH Teacher (TBD)</t>
+        </is>
+      </c>
+      <c r="J7" s="8" t="n"/>
+      <c r="K7" s="9" t="n"/>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>British Literature</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>Full-Year</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>Fall &amp; Spring</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="I8" s="7" t="inlineStr">
+        <is>
+          <t>New ENGLISH Teacher (TBD)</t>
+        </is>
+      </c>
+      <c r="J8" s="8" t="n"/>
+      <c r="K8" s="9" t="n"/>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>British Literature</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>Full-Year</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>Fall &amp; Spring</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="I9" s="7" t="inlineStr">
+        <is>
+          <t>New ENGLISH Teacher (TBD)</t>
+        </is>
+      </c>
+      <c r="J9" s="8" t="n"/>
+      <c r="K9" s="9" t="n"/>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>Creative Writing</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>Semester</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>Fall &amp; Spring</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="I10" s="7" t="inlineStr">
+        <is>
+          <t>New ENGLISH Teacher (TBD)</t>
+        </is>
+      </c>
+      <c r="J10" s="8" t="n"/>
+      <c r="K10" s="9" t="n"/>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t>Public Speaking</t>
+        </is>
+      </c>
+      <c r="C11" s="11" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="inlineStr">
+        <is>
+          <t>Semester</t>
+        </is>
+      </c>
+      <c r="E11" s="10" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="F11" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" s="10" t="inlineStr">
+        <is>
+          <t>Fall &amp; Spring</t>
+        </is>
+      </c>
+      <c r="H11" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="I11" s="7" t="inlineStr">
+        <is>
+          <t>New ENGLISH Teacher ELENA (TBD)</t>
+        </is>
+      </c>
+      <c r="J11" s="8" t="n"/>
+      <c r="K11" s="9" t="n"/>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>Public Speaking</t>
+        </is>
+      </c>
+      <c r="C12" s="11" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="inlineStr">
+        <is>
+          <t>Semester</t>
+        </is>
+      </c>
+      <c r="E12" s="10" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="F12" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="G12" s="10" t="inlineStr">
+        <is>
+          <t>Fall &amp; Spring</t>
+        </is>
+      </c>
+      <c r="H12" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="I12" s="7" t="inlineStr">
+        <is>
+          <t>New ENGLISH Teacher ELENA (TBD)</t>
+        </is>
+      </c>
+      <c r="J12" s="8" t="n"/>
+      <c r="K12" s="9" t="n"/>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>Public Speaking</t>
+        </is>
+      </c>
+      <c r="C13" s="11" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="inlineStr">
+        <is>
+          <t>Semester</t>
+        </is>
+      </c>
+      <c r="E13" s="10" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="F13" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="G13" s="10" t="inlineStr">
+        <is>
+          <t>Fall &amp; Spring</t>
+        </is>
+      </c>
+      <c r="H13" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>New ENGLISH Teacher ELENA (TBD)</t>
+        </is>
+      </c>
+      <c r="J13" s="8" t="n"/>
+      <c r="K13" s="9" t="n"/>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>Journalism</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>Semester</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>Fall &amp; Spring</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="I14" s="7" t="inlineStr">
+        <is>
+          <t>New ENGLISH Teacher (TBD)</t>
+        </is>
+      </c>
+      <c r="J14" s="8" t="n"/>
+      <c r="K14" s="9" t="n"/>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>Tech Theater Level 1</t>
+        </is>
+      </c>
+      <c r="C15" s="11" t="inlineStr">
+        <is>
+          <t>Theater Arts</t>
+        </is>
+      </c>
+      <c r="D15" s="10" t="inlineStr">
+        <is>
+          <t>Semester</t>
+        </is>
+      </c>
+      <c r="E15" s="10" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="F15" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" s="10" t="inlineStr">
+        <is>
+          <t>Fall &amp; Spring</t>
+        </is>
+      </c>
+      <c r="H15" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="I15" s="7" t="inlineStr">
+        <is>
+          <t>New THEATER Teacher (TBD)</t>
+        </is>
+      </c>
+      <c r="J15" s="8" t="n"/>
+      <c r="K15" s="9" t="n"/>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="B16" s="11" t="inlineStr">
+        <is>
+          <t>Adv Theater Production</t>
+        </is>
+      </c>
+      <c r="C16" s="11" t="inlineStr">
+        <is>
+          <t>Theater Arts</t>
+        </is>
+      </c>
+      <c r="D16" s="10" t="inlineStr">
+        <is>
+          <t>Full-Year</t>
+        </is>
+      </c>
+      <c r="E16" s="10" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="F16" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" s="10" t="inlineStr">
+        <is>
+          <t>Fall &amp; Spring</t>
+        </is>
+      </c>
+      <c r="H16" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="I16" s="7" t="inlineStr">
+        <is>
+          <t>New THEATER Teacher (TBD)</t>
+        </is>
+      </c>
+      <c r="J16" s="8" t="n"/>
+      <c r="K16" s="9" t="n"/>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>410</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>Algebra I</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>Mathematics</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>Full-Year</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>Fall &amp; Spring</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="I17" s="7" t="inlineStr">
+        <is>
+          <t>New MATH  Teacher OH (TBD)</t>
+        </is>
+      </c>
+      <c r="J17" s="8" t="n"/>
+      <c r="K17" s="9" t="n"/>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>410</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>Algebra I</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>Mathematics</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>Full-Year</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>Fall &amp; Spring</t>
+        </is>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="I18" s="7" t="inlineStr">
+        <is>
+          <t>New MATH  Teacher OH (TBD)</t>
+        </is>
+      </c>
+      <c r="J18" s="8" t="n"/>
+      <c r="K18" s="9" t="n"/>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>422</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>Geometry</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>Mathematics</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>Full-Year</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>Fall &amp; Spring</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="I19" s="7" t="inlineStr">
+        <is>
+          <t>New MATH  Teacher OH (TBD)</t>
+        </is>
+      </c>
+      <c r="J19" s="8" t="n"/>
+      <c r="K19" s="9" t="n"/>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>422</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>Geometry</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>Mathematics</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>Full-Year</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>Fall &amp; Spring</t>
+        </is>
+      </c>
+      <c r="H20" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="I20" s="7" t="inlineStr">
+        <is>
+          <t>New MATH  Teacher OH (TBD)</t>
+        </is>
+      </c>
+      <c r="J20" s="8" t="n"/>
+      <c r="K20" s="9" t="n"/>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>422</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>Geometry</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>Mathematics</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>Full-Year</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>Fall &amp; Spring</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="I21" s="7" t="inlineStr">
+        <is>
+          <t>New MATH  Teacher OH (TBD)</t>
+        </is>
+      </c>
+      <c r="J21" s="8" t="n"/>
+      <c r="K21" s="9" t="n"/>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="10" t="inlineStr">
+        <is>
+          <t>431</t>
+        </is>
+      </c>
+      <c r="B22" s="11" t="inlineStr">
+        <is>
+          <t>Algebra II/Trig H</t>
+        </is>
+      </c>
+      <c r="C22" s="11" t="inlineStr">
+        <is>
+          <t>Mathematics</t>
+        </is>
+      </c>
+      <c r="D22" s="10" t="inlineStr">
+        <is>
+          <t>Full-Year</t>
+        </is>
+      </c>
+      <c r="E22" s="10" t="inlineStr">
+        <is>
+          <t>Honors</t>
+        </is>
+      </c>
+      <c r="F22" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="G22" s="10" t="inlineStr">
+        <is>
+          <t>Fall &amp; Spring</t>
+        </is>
+      </c>
+      <c r="H22" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="I22" s="7" t="inlineStr">
+        <is>
+          <t>New MATH Teacher HARTMAN (TBD)</t>
+        </is>
+      </c>
+      <c r="J22" s="8" t="n"/>
+      <c r="K22" s="9" t="n"/>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="A23" s="10" t="inlineStr">
+        <is>
+          <t>440</t>
+        </is>
+      </c>
+      <c r="B23" s="11" t="inlineStr">
+        <is>
+          <t>Precalculus</t>
+        </is>
+      </c>
+      <c r="C23" s="11" t="inlineStr">
+        <is>
+          <t>Mathematics</t>
+        </is>
+      </c>
+      <c r="D23" s="10" t="inlineStr">
+        <is>
+          <t>Full-Year</t>
+        </is>
+      </c>
+      <c r="E23" s="10" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="F23" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="G23" s="10" t="inlineStr">
+        <is>
+          <t>Fall &amp; Spring</t>
+        </is>
+      </c>
+      <c r="H23" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="I23" s="7" t="inlineStr">
+        <is>
+          <t>New MATH Teacher HARTMAN (TBD)</t>
+        </is>
+      </c>
+      <c r="J23" s="8" t="n"/>
+      <c r="K23" s="9" t="n"/>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="A24" s="10" t="inlineStr">
+        <is>
+          <t>440</t>
+        </is>
+      </c>
+      <c r="B24" s="11" t="inlineStr">
+        <is>
+          <t>Precalculus</t>
+        </is>
+      </c>
+      <c r="C24" s="11" t="inlineStr">
+        <is>
+          <t>Mathematics</t>
+        </is>
+      </c>
+      <c r="D24" s="10" t="inlineStr">
+        <is>
+          <t>Full-Year</t>
+        </is>
+      </c>
+      <c r="E24" s="10" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="F24" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="G24" s="10" t="inlineStr">
+        <is>
+          <t>Fall &amp; Spring</t>
+        </is>
+      </c>
+      <c r="H24" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="I24" s="7" t="inlineStr">
+        <is>
+          <t>New MATH Teacher HARTMAN (TBD)</t>
+        </is>
+      </c>
+      <c r="J24" s="8" t="n"/>
+      <c r="K24" s="9" t="n"/>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="A25" s="10" t="inlineStr">
+        <is>
+          <t>450</t>
+        </is>
+      </c>
+      <c r="B25" s="11" t="inlineStr">
+        <is>
+          <t>Calculus H</t>
+        </is>
+      </c>
+      <c r="C25" s="11" t="inlineStr">
+        <is>
+          <t>Mathematics</t>
+        </is>
+      </c>
+      <c r="D25" s="10" t="inlineStr">
+        <is>
+          <t>Full-Year</t>
+        </is>
+      </c>
+      <c r="E25" s="10" t="inlineStr">
+        <is>
+          <t>Honors</t>
+        </is>
+      </c>
+      <c r="F25" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G25" s="10" t="inlineStr">
+        <is>
+          <t>Fall &amp; Spring</t>
+        </is>
+      </c>
+      <c r="H25" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="I25" s="7" t="inlineStr">
+        <is>
+          <t>New MATH Teacher HARTMAN (TBD)</t>
+        </is>
+      </c>
+      <c r="J25" s="8" t="n"/>
+      <c r="K25" s="9" t="n"/>
+    </row>
+    <row r="26" ht="22" customHeight="1">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>810</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>Theology 9</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>Theology</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>Full-Year</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="G26" s="5" t="inlineStr">
+        <is>
+          <t>Fall &amp; Spring</t>
+        </is>
+      </c>
+      <c r="H26" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="I26" s="7" t="inlineStr">
+        <is>
+          <t>New THEO 1 Teacher (TBD)</t>
+        </is>
+      </c>
+      <c r="J26" s="8" t="n"/>
+      <c r="K26" s="9" t="n"/>
+    </row>
+    <row r="27" ht="22" customHeight="1">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>810</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>Theology 9</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>Theology</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>Full-Year</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>Fall &amp; Spring</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="I27" s="7" t="inlineStr">
+        <is>
+          <t>New THEO 1 Teacher (TBD)</t>
+        </is>
+      </c>
+      <c r="J27" s="8" t="n"/>
+      <c r="K27" s="9" t="n"/>
+    </row>
+    <row r="28" ht="22" customHeight="1">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>810</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>Theology 9</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>Theology</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>Full-Year</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="G28" s="5" t="inlineStr">
+        <is>
+          <t>Fall &amp; Spring</t>
+        </is>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="I28" s="7" t="inlineStr">
+        <is>
+          <t>New THEO 1 Teacher (TBD)</t>
+        </is>
+      </c>
+      <c r="J28" s="8" t="n"/>
+      <c r="K28" s="9" t="n"/>
+    </row>
+    <row r="29" ht="22" customHeight="1">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>820</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>Theology 10</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>Theology</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>Full-Year</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>Fall &amp; Spring</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="I29" s="7" t="inlineStr">
+        <is>
+          <t>New THEO 1 Teacher (TBD)</t>
+        </is>
+      </c>
+      <c r="J29" s="8" t="n"/>
+      <c r="K29" s="9" t="n"/>
+    </row>
+    <row r="30" ht="22" customHeight="1">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>820</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>Theology 10</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>Theology</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>Full-Year</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="G30" s="5" t="inlineStr">
+        <is>
+          <t>Fall &amp; Spring</t>
+        </is>
+      </c>
+      <c r="H30" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="I30" s="7" t="inlineStr">
+        <is>
+          <t>New THEO 1 Teacher (TBD)</t>
+        </is>
+      </c>
+      <c r="J30" s="8" t="n"/>
+      <c r="K30" s="9" t="n"/>
+    </row>
+    <row r="31" ht="22" customHeight="1">
+      <c r="A31" s="10" t="inlineStr">
+        <is>
+          <t>830</t>
+        </is>
+      </c>
+      <c r="B31" s="11" t="inlineStr">
+        <is>
+          <t>Theology 11</t>
+        </is>
+      </c>
+      <c r="C31" s="11" t="inlineStr">
+        <is>
+          <t>Theology</t>
+        </is>
+      </c>
+      <c r="D31" s="10" t="inlineStr">
+        <is>
+          <t>Full-Year</t>
+        </is>
+      </c>
+      <c r="E31" s="10" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="F31" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="G31" s="10" t="inlineStr">
+        <is>
+          <t>Fall &amp; Spring</t>
+        </is>
+      </c>
+      <c r="H31" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="I31" s="7" t="inlineStr">
+        <is>
+          <t>New THEO 2 Teacher (TBD)</t>
+        </is>
+      </c>
+      <c r="J31" s="8" t="n"/>
+      <c r="K31" s="9" t="n"/>
+    </row>
+    <row r="32" ht="22" customHeight="1">
+      <c r="A32" s="10" t="inlineStr">
+        <is>
+          <t>849</t>
+        </is>
+      </c>
+      <c r="B32" s="11" t="inlineStr">
+        <is>
+          <t>Catholic Social Teaching</t>
+        </is>
+      </c>
+      <c r="C32" s="11" t="inlineStr">
+        <is>
+          <t>Theology</t>
+        </is>
+      </c>
+      <c r="D32" s="10" t="inlineStr">
+        <is>
+          <t>Semester</t>
+        </is>
+      </c>
+      <c r="E32" s="10" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="F32" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G32" s="10" t="inlineStr">
+        <is>
+          <t>Fall &amp; Spring</t>
+        </is>
+      </c>
+      <c r="H32" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="I32" s="7" t="inlineStr">
+        <is>
+          <t>New THEO 2 Teacher (TBD)</t>
+        </is>
+      </c>
+      <c r="J32" s="8" t="n"/>
+      <c r="K32" s="9" t="n"/>
+    </row>
+    <row r="33" ht="22" customHeight="1">
+      <c r="A33" s="10" t="inlineStr">
+        <is>
+          <t>849</t>
+        </is>
+      </c>
+      <c r="B33" s="11" t="inlineStr">
+        <is>
+          <t>Catholic Social Teaching</t>
+        </is>
+      </c>
+      <c r="C33" s="11" t="inlineStr">
+        <is>
+          <t>Theology</t>
+        </is>
+      </c>
+      <c r="D33" s="10" t="inlineStr">
+        <is>
+          <t>Semester</t>
+        </is>
+      </c>
+      <c r="E33" s="10" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="F33" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="G33" s="10" t="inlineStr">
+        <is>
+          <t>Fall &amp; Spring</t>
+        </is>
+      </c>
+      <c r="H33" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="I33" s="7" t="inlineStr">
+        <is>
+          <t>New THEO 2 Teacher (TBD)</t>
+        </is>
+      </c>
+      <c r="J33" s="8" t="n"/>
+      <c r="K33" s="9" t="n"/>
+    </row>
+    <row r="34" ht="22" customHeight="1">
+      <c r="A34" s="10" t="inlineStr">
+        <is>
+          <t>849</t>
+        </is>
+      </c>
+      <c r="B34" s="11" t="inlineStr">
+        <is>
+          <t>Catholic Social Teaching</t>
+        </is>
+      </c>
+      <c r="C34" s="11" t="inlineStr">
+        <is>
+          <t>Theology</t>
+        </is>
+      </c>
+      <c r="D34" s="10" t="inlineStr">
+        <is>
+          <t>Semester</t>
+        </is>
+      </c>
+      <c r="E34" s="10" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="F34" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="G34" s="10" t="inlineStr">
+        <is>
+          <t>Fall &amp; Spring</t>
+        </is>
+      </c>
+      <c r="H34" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="I34" s="7" t="inlineStr">
+        <is>
+          <t>New THEO 2 Teacher (TBD)</t>
+        </is>
+      </c>
+      <c r="J34" s="8" t="n"/>
+      <c r="K34" s="9" t="n"/>
+    </row>
+    <row r="35" ht="22" customHeight="1">
+      <c r="A35" s="10" t="inlineStr">
+        <is>
+          <t>849</t>
+        </is>
+      </c>
+      <c r="B35" s="11" t="inlineStr">
+        <is>
+          <t>Catholic Social Teaching</t>
+        </is>
+      </c>
+      <c r="C35" s="11" t="inlineStr">
+        <is>
+          <t>Theology</t>
+        </is>
+      </c>
+      <c r="D35" s="10" t="inlineStr">
+        <is>
+          <t>Semester</t>
+        </is>
+      </c>
+      <c r="E35" s="10" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="F35" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="G35" s="10" t="inlineStr">
+        <is>
+          <t>Fall &amp; Spring</t>
+        </is>
+      </c>
+      <c r="H35" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="I35" s="7" t="inlineStr">
+        <is>
+          <t>New THEO 2 Teacher (TBD)</t>
+        </is>
+      </c>
+      <c r="J35" s="8" t="n"/>
+      <c r="K35" s="9" t="n"/>
+    </row>
+    <row r="36" ht="22" customHeight="1">
+      <c r="A36" s="10" t="inlineStr">
+        <is>
+          <t>849</t>
+        </is>
+      </c>
+      <c r="B36" s="11" t="inlineStr">
+        <is>
+          <t>Catholic Social Teaching</t>
+        </is>
+      </c>
+      <c r="C36" s="11" t="inlineStr">
+        <is>
+          <t>Theology</t>
+        </is>
+      </c>
+      <c r="D36" s="10" t="inlineStr">
+        <is>
+          <t>Semester</t>
+        </is>
+      </c>
+      <c r="E36" s="10" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="F36" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="G36" s="10" t="inlineStr">
+        <is>
+          <t>Fall &amp; Spring</t>
+        </is>
+      </c>
+      <c r="H36" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="I36" s="7" t="inlineStr">
+        <is>
+          <t>New THEO 2 Teacher (TBD)</t>
+        </is>
+      </c>
+      <c r="J36" s="8" t="n"/>
+      <c r="K36" s="9" t="n"/>
+    </row>
+    <row r="37" ht="22" customHeight="1">
+      <c r="A37" s="10" t="inlineStr">
+        <is>
+          <t>849</t>
+        </is>
+      </c>
+      <c r="B37" s="11" t="inlineStr">
+        <is>
+          <t>Catholic Social Teaching</t>
+        </is>
+      </c>
+      <c r="C37" s="11" t="inlineStr">
+        <is>
+          <t>Theology</t>
+        </is>
+      </c>
+      <c r="D37" s="10" t="inlineStr">
+        <is>
+          <t>Semester</t>
+        </is>
+      </c>
+      <c r="E37" s="10" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="F37" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="G37" s="10" t="inlineStr">
+        <is>
+          <t>Fall &amp; Spring</t>
+        </is>
+      </c>
+      <c r="H37" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="I37" s="7" t="inlineStr">
+        <is>
+          <t>New THEO 2 Teacher (TBD)</t>
+        </is>
+      </c>
+      <c r="J37" s="8" t="n"/>
+      <c r="K37" s="9" t="n"/>
+    </row>
+    <row r="38" ht="22" customHeight="1">
+      <c r="A38" s="10" t="inlineStr">
+        <is>
+          <t>849</t>
+        </is>
+      </c>
+      <c r="B38" s="11" t="inlineStr">
+        <is>
+          <t>Catholic Social Teaching</t>
+        </is>
+      </c>
+      <c r="C38" s="11" t="inlineStr">
+        <is>
+          <t>Theology</t>
+        </is>
+      </c>
+      <c r="D38" s="10" t="inlineStr">
+        <is>
+          <t>Semester</t>
+        </is>
+      </c>
+      <c r="E38" s="10" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="F38" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="G38" s="10" t="inlineStr">
+        <is>
+          <t>Fall &amp; Spring</t>
+        </is>
+      </c>
+      <c r="H38" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="I38" s="7" t="inlineStr">
+        <is>
+          <t>New THEO 2 Teacher (TBD)</t>
+        </is>
+      </c>
+      <c r="J38" s="8" t="n"/>
+      <c r="K38" s="9" t="n"/>
+    </row>
+    <row r="39" ht="22" customHeight="1">
+      <c r="A39" s="10" t="inlineStr">
+        <is>
+          <t>849</t>
+        </is>
+      </c>
+      <c r="B39" s="11" t="inlineStr">
+        <is>
+          <t>Catholic Social Teaching</t>
+        </is>
+      </c>
+      <c r="C39" s="11" t="inlineStr">
+        <is>
+          <t>Theology</t>
+        </is>
+      </c>
+      <c r="D39" s="10" t="inlineStr">
+        <is>
+          <t>Semester</t>
+        </is>
+      </c>
+      <c r="E39" s="10" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="F39" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="G39" s="10" t="inlineStr">
+        <is>
+          <t>Fall &amp; Spring</t>
+        </is>
+      </c>
+      <c r="H39" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="I39" s="7" t="inlineStr">
+        <is>
+          <t>New THEO 2 Teacher (TBD)</t>
+        </is>
+      </c>
+      <c r="J39" s="8" t="n"/>
+      <c r="K39" s="9" t="n"/>
+    </row>
+    <row r="40" ht="22" customHeight="1">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>955</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>Academic Support</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>Special Education</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>Full-Year</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="F40" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="G40" s="5" t="inlineStr">
+        <is>
+          <t>Fall &amp; Spring</t>
+        </is>
+      </c>
+      <c r="H40" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="I40" s="7" t="inlineStr">
+        <is>
+          <t>New LN Teacher (TBD)</t>
+        </is>
+      </c>
+      <c r="J40" s="8" t="n"/>
+      <c r="K40" s="9" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="12" t="inlineStr">
+        <is>
+          <t>SUMMARY: 35 sections across 8 TBD placeholders need teacher assignments</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="13" t="inlineStr">
+        <is>
+          <t>Placeholder</t>
+        </is>
+      </c>
+      <c r="D44" s="13" t="inlineStr">
+        <is>
           <t>Sections</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>Requests</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>CONFIRMED TEACHER NAME</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>NOTES</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="60" customHeight="1">
-      <c r="A6" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
+    </row>
+    <row r="45">
+      <c r="B45" s="14" t="inlineStr">
         <is>
           <t>New ENGLISH Teacher (TBD)</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>British Literature (130) — 5 sec
-British Literature (132) — 1 sec
-Creative Writing (143) — 1 sec
-Journalism (145) — 1 sec</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="F6" s="5" t="n">
-        <v>117</v>
-      </c>
-      <c r="G6" s="8" t="inlineStr"/>
-      <c r="H6" s="8" t="inlineStr"/>
-    </row>
-    <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="B7" s="10" t="inlineStr">
+      <c r="D45" s="15" t="inlineStr">
+        <is>
+          <t>6 sections: Brit Lit (130) ×3, Brit Lit (132) ×1, Creative Writing (143) ×1, Journalism (145) ×1</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" s="14" t="inlineStr">
         <is>
           <t>New ENGLISH Teacher ELENA (TBD)</t>
         </is>
       </c>
-      <c r="C7" s="9" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="D7" s="11" t="inlineStr">
-        <is>
-          <t>Public Speaking (144) — 3 sec</t>
-        </is>
-      </c>
-      <c r="E7" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="F7" s="9" t="n">
-        <v>47</v>
-      </c>
-      <c r="G7" s="8" t="inlineStr"/>
-      <c r="H7" s="8" t="inlineStr"/>
-    </row>
-    <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="D46" s="15" t="inlineStr">
+        <is>
+          <t>3 sections: Public Speaking (144) ×3</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="14" t="inlineStr">
         <is>
           <t>New LN Teacher (TBD)</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>Special Education</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>Academic Support (955) — 4 sec</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="F8" s="5" t="n">
-        <v>28</v>
-      </c>
-      <c r="G8" s="8" t="inlineStr"/>
-      <c r="H8" s="8" t="inlineStr"/>
-    </row>
-    <row r="9" ht="60" customHeight="1">
-      <c r="A9" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="B9" s="10" t="inlineStr">
+      <c r="D47" s="15" t="inlineStr">
+        <is>
+          <t>1 section: Academic Support (955) ×1</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" s="14" t="inlineStr">
         <is>
           <t>New MATH Teacher OH (TBD)</t>
         </is>
       </c>
-      <c r="C9" s="9" t="inlineStr">
-        <is>
-          <t>Mathematics</t>
-        </is>
-      </c>
-      <c r="D9" s="11" t="inlineStr">
-        <is>
-          <t>Algebra I (410) — 5 sec
-Geometry (422) — 3 sec</t>
-        </is>
-      </c>
-      <c r="E9" s="9" t="n">
-        <v>8</v>
-      </c>
-      <c r="F9" s="9" t="n">
-        <v>131</v>
-      </c>
-      <c r="G9" s="8" t="inlineStr"/>
-      <c r="H9" s="8" t="inlineStr"/>
-    </row>
-    <row r="10" ht="60" customHeight="1">
-      <c r="A10" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="D48" s="15" t="inlineStr">
+        <is>
+          <t>5 sections: Algebra I (410) ×2, Geometry (422) ×3</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" s="14" t="inlineStr">
         <is>
           <t>New MATH Teacher HARTMAN (TBD)</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>Mathematics</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>Algebra II/Trig H (431) — 3 sec
-Precalculus (440) — 5 sec
-Calculus H (450) — 1 sec</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="F10" s="5" t="n">
-        <v>187</v>
-      </c>
-      <c r="G10" s="8" t="inlineStr"/>
-      <c r="H10" s="8" t="inlineStr"/>
-    </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="B11" s="10" t="inlineStr">
+      <c r="D49" s="15" t="inlineStr">
+        <is>
+          <t>4 sections: Alg II/Trig H (431) ×1, Precalculus (440) ×2, Calculus H (450) ×1</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="14" t="inlineStr">
         <is>
           <t>New THEATER Teacher (TBD)</t>
         </is>
       </c>
-      <c r="C11" s="9" t="inlineStr">
-        <is>
-          <t>Theater Arts</t>
-        </is>
-      </c>
-      <c r="D11" s="11" t="inlineStr">
-        <is>
-          <t>Tech Theater Level 1 (225) — 1 sec
-Adv Theater Production (228) — 1 sec</t>
-        </is>
-      </c>
-      <c r="E11" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="F11" s="9" t="n">
-        <v>9</v>
-      </c>
-      <c r="G11" s="8" t="inlineStr"/>
-      <c r="H11" s="8" t="inlineStr"/>
-    </row>
-    <row r="12" ht="60" customHeight="1">
-      <c r="A12" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="D50" s="15" t="inlineStr">
+        <is>
+          <t>2 sections: Tech Theater (225) ×1, Adv Theater (228) ×1</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="14" t="inlineStr">
         <is>
           <t>New THEO 1 Teacher (TBD)</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>Theology</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>Theology 9 (810) — 9 sec
-Theology 10 (820) — 9 sec</t>
-        </is>
-      </c>
-      <c r="E12" s="5" t="n">
-        <v>18</v>
-      </c>
-      <c r="F12" s="5" t="n">
-        <v>435</v>
-      </c>
-      <c r="G12" s="8" t="inlineStr"/>
-      <c r="H12" s="8" t="inlineStr"/>
-    </row>
-    <row r="13" ht="60" customHeight="1">
-      <c r="A13" s="9" t="n">
-        <v>8</v>
-      </c>
-      <c r="B13" s="10" t="inlineStr">
+      <c r="D51" s="15" t="inlineStr">
+        <is>
+          <t>5 sections: Theology 9 (810) ×3, Theology 10 (820) ×2</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" s="14" t="inlineStr">
         <is>
           <t>New THEO 2 Teacher (TBD)</t>
         </is>
       </c>
-      <c r="C13" s="9" t="inlineStr">
-        <is>
-          <t>Theology</t>
-        </is>
-      </c>
-      <c r="D13" s="11" t="inlineStr">
-        <is>
-          <t>Theology 11 (830) — 9 sec
-Catholic Social Teaching (849) — 8 sec</t>
-        </is>
-      </c>
-      <c r="E13" s="9" t="n">
-        <v>17</v>
-      </c>
-      <c r="F13" s="9" t="n">
-        <v>365</v>
-      </c>
-      <c r="G13" s="8" t="inlineStr"/>
-      <c r="H13" s="8" t="inlineStr"/>
+      <c r="D52" s="15" t="inlineStr">
+        <is>
+          <t>9 sections: Theology 11 (830) ×1, Catholic Social Teaching (849) ×8</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="65" customHeight="1">
+      <c r="A54" s="16" t="inlineStr">
+        <is>
+          <t>TIPS: (1) If one new hire replaces one placeholder, select the same name for all rows with that placeholder. (2) If a placeholder's load is being SPLIT between two teachers, assign each section to the correct teacher individually. (3) Existing teachers can pick up additional sections — just select their name from the dropdown. (4) If a hire is truly new and not on the list, select "NEW HIRE" from the dropdown and type their full name (Last, First) in the Notes column.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="23">
+    <mergeCell ref="D50:K50"/>
+    <mergeCell ref="D44:K44"/>
+    <mergeCell ref="B47:C47"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="D46:K46"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="D45:K45"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="D52:K52"/>
+    <mergeCell ref="A54:K54"/>
+    <mergeCell ref="D49:K49"/>
+    <mergeCell ref="D48:K48"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="D47:K47"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="B51:C51"/>
+    <mergeCell ref="A43:K43"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="D51:K51"/>
+    <mergeCell ref="B50:C50"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation sqref="J6 J7 J8 J9 J10 J11 J12 J13 J14 J15 J16 J17 J18 J19 J20 J21 J22 J23 J24 J25 J26 J27 J28 J29 J30 J31 J32 J33 J34 J35 J36 J37 J38 J39 J40" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Teacher" error="Please select a teacher from the dropdown list, or choose &quot;NEW HIRE&quot; and enter the name in the Notes column." promptTitle="Select Teacher" prompt="Choose a confirmed teacher from the dropdown. For a new hire not on the list, select &quot;NEW HIRE&quot; and type the full name in the Notes column." type="list">
+      <formula1>TeacherList</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A57"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="45" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="17" t="inlineStr">
+        <is>
+          <t>CONFIRMED TEACHERS</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="18" t="inlineStr">
+        <is>
+          <t>NEW HIRE (enter name in Notes column)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="19" t="inlineStr">
+        <is>
+          <t>Ahn, Keun</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>Angotti, Sylvia</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>Arcede, Francis</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>Biggs, Tyrell</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>Calidas, Riddhi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>Campbell, Scott</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>Carr, Lynette</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>Chiaravalloti, Michael</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>Connelly, Tiffany</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>Corcoran, Kevin</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>Daniels, Torrence</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>DeLeon, Marco</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="12" t="inlineStr">
-        <is>
-          <t>INSTRUCTIONS</t>
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>Delmonico, Marisa</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="13" t="inlineStr">
-        <is>
-          <t>1. Fill in Column G (yellow cells) with the confirmed hire name for each placeholder.</t>
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>Dennehy, Sheri</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="13" t="inlineStr">
-        <is>
-          <t>2. Use Column H (Notes) for any additional context — e.g., "Part-time, available periods A-D only" or "Splitting load with [other teacher]".</t>
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>Doughty, Chelsea</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="13" t="inlineStr">
-        <is>
-          <t>3. If a single hire is replacing the placeholder, enter their full name (Last, First) in Column G.</t>
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>Dwyer, Kevin</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="13" t="inlineStr">
-        <is>
-          <t>4. If the load is being SPLIT across multiple teachers, enter the primary teacher in Column G and explain the split in Column H.</t>
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>Esposito, John</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="13" t="inlineStr">
-        <is>
-          <t>5. If a position is still unfilled, leave Column G blank and note the expected hire date in Column H.</t>
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>Fisk, Mary Pat</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>6. Rows #7 and #8 (Theology) show 18 and 17 sections — these are likely shared across multiple teachers. Please clarify.</t>
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>Gerlach, Reese</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="13" t="inlineStr">
-        <is>
-          <t>7. Return this file and the engine will update all references, recalculate load balancing, and re-run the schedule.</t>
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>Gettler, Mary</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>Guy, Libbie</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="12" t="inlineStr">
-        <is>
-          <t>IMPACT SUMMARY</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="40" customHeight="1">
-      <c r="A25" s="14" t="inlineStr">
-        <is>
-          <t>8 placeholder teachers cover 69 sections serving 1,319 student requests. Resolving these will eliminate artificial load violations, improve teacher-conflict detection accuracy, and may reduce the current 351 clash count.</t>
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>Hampson, Elizabeth</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>Harris, Megan</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>Janeczko, Douglas</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="15" t="inlineStr">
-        <is>
-          <t>EXAMPLE — How to fill in:</t>
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>Judge, Michelle</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="16" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B28" s="16" t="inlineStr">
-        <is>
-          <t>Current Placeholder</t>
-        </is>
-      </c>
-      <c r="C28" s="16" t="inlineStr">
-        <is>
-          <t>Department</t>
-        </is>
-      </c>
-      <c r="D28" s="16" t="inlineStr">
-        <is>
-          <t>Courses Assigned</t>
-        </is>
-      </c>
-      <c r="E28" s="16" t="inlineStr">
-        <is>
-          <t>Sections</t>
-        </is>
-      </c>
-      <c r="F28" s="16" t="inlineStr">
-        <is>
-          <t>Requests</t>
-        </is>
-      </c>
-      <c r="G28" s="16" t="inlineStr">
-        <is>
-          <t>CONFIRMED TEACHER NAME</t>
-        </is>
-      </c>
-      <c r="H28" s="16" t="inlineStr">
-        <is>
-          <t>NOTES</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="45" customHeight="1">
-      <c r="A29" s="17" t="inlineStr">
-        <is>
-          <t>Ex.</t>
-        </is>
-      </c>
-      <c r="B29" s="18" t="inlineStr">
-        <is>
-          <t>New MATH Teacher OH (TBD)</t>
-        </is>
-      </c>
-      <c r="C29" s="17" t="inlineStr">
-        <is>
-          <t>Mathematics</t>
-        </is>
-      </c>
-      <c r="D29" s="18" t="inlineStr">
-        <is>
-          <t>Algebra I (410) — 5 sec
-Geometry (422) — 3 sec</t>
-        </is>
-      </c>
-      <c r="E29" s="17" t="n">
-        <v>8</v>
-      </c>
-      <c r="F29" s="17" t="n">
-        <v>131</v>
-      </c>
-      <c r="G29" s="19" t="inlineStr">
-        <is>
-          <t>Rodriguez, Maria</t>
-        </is>
-      </c>
-      <c r="H29" s="20" t="inlineStr">
-        <is>
-          <t>Full-time hire, starts Aug 15. Available all periods.</t>
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>Kilduff, Kevin</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>Konopelski, Louis</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>Kozak, Bernadette</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>Langan, John</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t>Laracy, John</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="19" t="inlineStr">
+        <is>
+          <t>Lomascolo, Frank</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="19" t="inlineStr">
+        <is>
+          <t>Lopez, Enrique</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="19" t="inlineStr">
+        <is>
+          <t>Martino, Brianna</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="19" t="inlineStr">
+        <is>
+          <t>Mazella, Julie</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="19" t="inlineStr">
+        <is>
+          <t>McConnell, George</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="19" t="inlineStr">
+        <is>
+          <t>McManus, Brianna</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="19" t="inlineStr">
+        <is>
+          <t>Montegari, James</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="19" t="inlineStr">
+        <is>
+          <t>Muscat, Nicole</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="19" t="inlineStr">
+        <is>
+          <t>Nepolitan, John</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="19" t="inlineStr">
+        <is>
+          <t>Nobilione, Lauren</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="19" t="inlineStr">
+        <is>
+          <t>O'Connor, Paul</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="19" t="inlineStr">
+        <is>
+          <t>Ojo, Clement</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="19" t="inlineStr">
+        <is>
+          <t>Park, Sam</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="19" t="inlineStr">
+        <is>
+          <t>Quast, Richard</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="19" t="inlineStr">
+        <is>
+          <t>Ramirez, Jaime</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="19" t="inlineStr">
+        <is>
+          <t>Sabella, Daniel</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="19" t="inlineStr">
+        <is>
+          <t>Saggio, Jack</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="19" t="inlineStr">
+        <is>
+          <t>Serra, Carmine</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="19" t="inlineStr">
+        <is>
+          <t>Stoller, Timothy</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="19" t="inlineStr">
+        <is>
+          <t>Tranate, John</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="19" t="inlineStr">
+        <is>
+          <t>Tuesta, David</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="19" t="inlineStr">
+        <is>
+          <t>Willi, Mary</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="19" t="inlineStr">
+        <is>
+          <t>Winters, Jack</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="19" t="inlineStr">
+        <is>
+          <t>Zawacki, Richard</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="19" t="inlineStr">
+        <is>
+          <t>Zawiski, Brian</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="14">
-    <mergeCell ref="A18:H18"/>
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A21:H21"/>
-    <mergeCell ref="A15:H15"/>
-    <mergeCell ref="A25:H25"/>
-    <mergeCell ref="A20:H20"/>
-    <mergeCell ref="A24:H24"/>
-    <mergeCell ref="A16:H16"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A19:H19"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A27:H27"/>
-    <mergeCell ref="A22:H22"/>
-    <mergeCell ref="A17:H17"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>